--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Google Cloud Data Architect &amp; IAM Data Modernization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101b904e03cc0a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a876f1d70bf86df</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd76c0defb4382</t>
+          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bbd2a751aa54c1</t>
+          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps and Cloud Engineer</t>
+          <t>Senior IT Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=792a6691e358ff5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Software Engineer, 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Finance Data Mart - Domain Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,235 +863,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LoadUp Technologies</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6e5d4c8040aea</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DATA ENGINEER II</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sony Pictures Entertainment</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Culver City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior QA Analyst/Software</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Labcorp</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, Scala, DynamoDB, Splunk, Jenkins, Jenkins, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a397b75b31e4442d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IT Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00f41d32e3dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, 1</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, Docker</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bacd10e684dc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Elekta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,85 +801,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Finance Data Mart - Domain Data Architect</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=216cf9bc02e5f50a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DataOps Engineer (Local to Charlotte, NC)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffddefbdd0be19</t>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6063e836c57f9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (Local to Charlotte, NC)</t>
+          <t>Sr Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213d2103202cab40</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior Sales Automation &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -705,111 +705,6 @@
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,140 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Engineer - Operations Improvement</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, MongoDB, ETL, Tableau, Splunk, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ba5c9bd83fc8ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad5a01749b44d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Sales Automation &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8721cb25b26868</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2bac108848ff31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,112 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9428fe1d5deac146</t>
+          <t>https://www.indeed.com/viewjob?jk=f422e5e1f7c77012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Senior AI/ML Scientist</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>General Motors (GM)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Milford, MI, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b457a11e98e82c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,50 +626,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
         </is>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,15 +626,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
         </is>

--- a/results/job_matches_2026-05-24.xlsx
+++ b/results/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
@@ -672,6 +672,41 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>
